--- a/artfynd/A 33763-2024 artfynd.xlsx
+++ b/artfynd/A 33763-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119820484</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33763-2024 artfynd.xlsx
+++ b/artfynd/A 33763-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820484</v>
+        <v>127020036</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721815</v>
+        <v>721553</v>
       </c>
       <c r="R2" t="n">
-        <v>7216290</v>
+        <v>7216275</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +773,125 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119820484</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>721815</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7216290</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
